--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64930_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64930_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3bde07ea908d455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re832bfdaaef042be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.2197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2889</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.1712</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64930_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64930_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re832bfdaaef042be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra08eaec0b9344d4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3655</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.9179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.4907</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.9414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.5881</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.8354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.5549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8531</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.3092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.1557</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.4784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.7740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.7040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8871</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.5044</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.3452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.2351</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.6303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.7868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.8976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9297</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.6379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.0345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
